--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.165" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.165" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.165.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.165.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0165.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0165.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.165" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.165" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y68"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22 â€” 23</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Re-Engrossment â€”in what cases</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]158</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]158</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 158</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: #</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]158</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -636,7 +640,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Application how made</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,24 +680,24 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Re-Engrossment â€” in what - cases</t>
+          <t>L52: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22â€”23</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L10: isolated marker/symbol line :: 20</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 20</t>
+          <t>L38: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -731,24 +739,24 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23 â€” 113</t>
+          <t>L75: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23â€”113</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L12: isolated marker/symbol line :: .</t>
+          <t>L10: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 21</t>
+          <t>L40: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -774,7 +782,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -790,24 +798,24 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L143: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: May be confined to short Statement . . •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L13: isolated marker/symbol line :: 21</t>
+          <t>L12: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 22</t>
+          <t>L42: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -849,24 +857,24 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22 â€” 23</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+4EBA CJK UNIFIED IDEOGRAPH-4EBA | isolated marker/symbol line :: 人</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Application how made</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L17: isolated marker/symbol line :: 22</t>
+          <t>L13: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: #</t>
+          <t>L46: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -906,26 +914,22 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Re-Engrossment â€” in what - cases</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: May be confined to short Statement . . â€¢</t>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L21: isolated marker/symbol line :: 23</t>
+          <t>L17: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 23</t>
+          <t>L48: symbol-only separator/garbage line :: 22—23</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -965,26 +969,22 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23 â€” 113</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Application how made</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: 23</t>
+          <t>L19: symbol-only separator/garbage line :: 22 — 23</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 23</t>
+          <t>L50: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1020,26 +1020,22 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: .</t>
+          <t>L21: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 24</t>
+          <t>L52: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1061,12 +1057,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1078,19 +1074,19 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 41â€”42</t>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L26: isolated marker/symbol line :: 24</t>
+          <t>L23: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 24</t>
+          <t>L54: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1117,7 +1113,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1129,19 +1125,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L165: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • / 42</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: 24</t>
+          <t>L25: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: H(</t>
+          <t>L56: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1163,12 +1159,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1180,19 +1176,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: Y</t>
+          <t>L26: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: C&lt;</t>
+          <t>L58: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1231,19 +1227,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 110</t>
+          <t>L28: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: N</t>
+          <t>L60: symbol-only separator/garbage line :: 23—113</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1270,7 +1266,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1282,19 +1278,19 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ / 42</t>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 40</t>
+          <t>L30: symbol-only separator/garbage line :: 23 — 113</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: T</t>
+          <t>L63: isolated marker/symbol line :: H(</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1333,19 +1329,19 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢</t>
+          <t>L194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 40</t>
+          <t>L32: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: O</t>
+          <t>L66: isolated marker/symbol line :: C&lt;</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1382,21 +1378,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 40</t>
+          <t>L34: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: E</t>
+          <t>L67: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1433,21 +1425,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 41</t>
+          <t>L37: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: E</t>
+          <t>L75: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1472,21 +1460,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 41</t>
+          <t>L39: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: P</t>
+          <t>L76: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1516,12 +1500,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 41</t>
+          <t>L41: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: P</t>
+          <t>L77: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1551,12 +1535,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 41</t>
+          <t>L43: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: T</t>
+          <t>L78: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1586,12 +1570,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 41</t>
+          <t>L45: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: -</t>
+          <t>L80: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1621,12 +1605,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L47: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 0</t>
+          <t>L84: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1656,12 +1640,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L54: symbol-only separator/garbage line :: 41-42</t>
+          <t>L49: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: N</t>
+          <t>L87: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1691,12 +1675,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 42</t>
+          <t>L51: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: A</t>
+          <t>L89: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1726,12 +1710,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 42</t>
+          <t>L52: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: s</t>
+          <t>L91: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1761,12 +1745,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 43</t>
+          <t>L54: symbol-only separator/garbage line :: 41-42</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L93: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1796,12 +1780,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 43</t>
+          <t>L57: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L94: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1831,12 +1815,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 43</t>
+          <t>L59: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: f</t>
+          <t>L95: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1866,12 +1850,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 158</t>
+          <t>L61: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 110</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1901,12 +1885,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 8</t>
+          <t>L63: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: &gt;</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1936,12 +1920,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 20</t>
+          <t>L66: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L124: isolated marker/symbol line :: f</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1971,12 +1955,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: .</t>
+          <t>L69: isolated marker/symbol line :: 158</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L132: isolated marker/symbol line :: 40</t>
+          <t>L126: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2006,12 +1990,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: 21</t>
+          <t>L75: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 40</t>
+          <t>L128: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2041,12 +2025,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 22</t>
+          <t>L79: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 40</t>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2076,12 +2060,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 23</t>
+          <t>L81: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L138: symbol-only separator/garbage line :: 41.</t>
+          <t>L132: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2111,12 +2095,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: N</t>
+          <t>L84: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 41</t>
+          <t>L134: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2146,12 +2130,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: 23</t>
+          <t>L85: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 41</t>
+          <t>L136: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2181,12 +2165,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: .</t>
+          <t>L91: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L144: symbol-only separator/garbage line :: . 41</t>
+          <t>L138: symbol-only separator/garbage line :: 41.</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2216,12 +2200,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 24</t>
+          <t>L94: symbol-only separator/garbage line :: 22 — 23</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 41</t>
+          <t>L140: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2251,12 +2235,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 24</t>
+          <t>L97: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L142: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2286,12 +2270,12 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: O</t>
+          <t>L98: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L144: symbol-only separator/garbage line :: . 41</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2321,12 +2305,12 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: Y</t>
+          <t>L100: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L146: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2356,12 +2340,12 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: T</t>
+          <t>L103: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L164: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "43" vs "42 42 43X" :: 42 &gt;</t>
+          <t>L148: symbol-only separator/garbage line :: 41—42</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2391,12 +2375,12 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 110</t>
+          <t>L104: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2426,12 +2410,12 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: O</t>
+          <t>L107: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: 4</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2461,12 +2445,12 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: E</t>
+          <t>L108: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L183: isolated marker/symbol line :: 1</t>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2496,12 +2480,12 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 40</t>
+          <t>L110: symbol-only separator/garbage line :: 23 — 113</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L184: isolated marker/symbol line :: I</t>
+          <t>L164: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "43" vs "42 42 43X" :: 42 &gt;</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -2531,12 +2515,12 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: E</t>
+          <t>L113: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L186: isolated marker/symbol line :: 1</t>
+          <t>L165: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • / 42</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -2566,12 +2550,12 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 40</t>
+          <t>L114: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: 43</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -2601,12 +2585,12 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: P</t>
+          <t>L116: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -2636,12 +2620,12 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 40</t>
+          <t>L117: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L181: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -2671,10 +2655,14 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 41</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr"/>
+          <t>L119: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L183: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
       <c r="R52" s="1" t="inlineStr"/>
@@ -2702,10 +2690,14 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: P</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr"/>
+          <t>L121: isolated marker/symbol line :: 40</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L184: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
       <c r="R53" s="1" t="inlineStr"/>
@@ -2733,10 +2725,14 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: 41</t>
-        </is>
-      </c>
-      <c r="O54" s="1" t="inlineStr"/>
+          <t>L122: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L186: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
       <c r="R54" s="1" t="inlineStr"/>
@@ -2764,10 +2760,14 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 41</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr"/>
+          <t>L124: isolated marker/symbol line :: 40</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L188: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr"/>
       <c r="R55" s="1" t="inlineStr"/>
@@ -2795,10 +2795,14 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: T</t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="inlineStr"/>
+          <t>L125: isolated marker/symbol line :: P</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr"/>
       <c r="R56" s="1" t="inlineStr"/>
@@ -2826,10 +2830,14 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 41</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr"/>
+          <t>L127: isolated marker/symbol line :: 40</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
       <c r="R57" s="1" t="inlineStr"/>
@@ -2857,7 +2865,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 4</t>
+          <t>L130: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2888,7 +2896,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 41</t>
+          <t>L131: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2919,7 +2927,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L133: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2950,7 +2958,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L145: symbol-only separator/garbage line :: 41-42</t>
+          <t>L136: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2981,7 +2989,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: N</t>
+          <t>L137: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3012,7 +3020,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: 42</t>
+          <t>L139: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3043,7 +3051,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 42</t>
+          <t>L140: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3074,7 +3082,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 43</t>
+          <t>L142: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3105,7 +3113,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L156: isolated marker/symbol line :: 43</t>
+          <t>L143: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3136,7 +3144,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: 6</t>
+          <t>L145: symbol-only separator/garbage line :: 41-42</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3167,7 +3175,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: 43</t>
+          <t>L146: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3182,6 +3190,223 @@
       <c r="X68" s="1" t="inlineStr"/>
       <c r="Y68" s="1" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr"/>
+      <c r="B69" s="1" t="inlineStr"/>
+      <c r="C69" s="1" t="inlineStr"/>
+      <c r="D69" s="1" t="inlineStr"/>
+      <c r="E69" s="1" t="inlineStr"/>
+      <c r="F69" s="1" t="inlineStr"/>
+      <c r="G69" s="1" t="inlineStr"/>
+      <c r="H69" s="1" t="inlineStr"/>
+      <c r="I69" s="1" t="inlineStr"/>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
+      <c r="L69" s="1" t="inlineStr"/>
+      <c r="M69" s="1" t="inlineStr"/>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>L149: isolated marker/symbol line :: 42</t>
+        </is>
+      </c>
+      <c r="O69" s="1" t="inlineStr"/>
+      <c r="P69" s="1" t="inlineStr"/>
+      <c r="Q69" s="1" t="inlineStr"/>
+      <c r="R69" s="1" t="inlineStr"/>
+      <c r="S69" s="1" t="inlineStr"/>
+      <c r="T69" s="1" t="inlineStr"/>
+      <c r="U69" s="1" t="inlineStr"/>
+      <c r="V69" s="1" t="inlineStr"/>
+      <c r="W69" s="1" t="inlineStr"/>
+      <c r="X69" s="1" t="inlineStr"/>
+      <c r="Y69" s="1" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr"/>
+      <c r="B70" s="1" t="inlineStr"/>
+      <c r="C70" s="1" t="inlineStr"/>
+      <c r="D70" s="1" t="inlineStr"/>
+      <c r="E70" s="1" t="inlineStr"/>
+      <c r="F70" s="1" t="inlineStr"/>
+      <c r="G70" s="1" t="inlineStr"/>
+      <c r="H70" s="1" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr"/>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
+      <c r="L70" s="1" t="inlineStr"/>
+      <c r="M70" s="1" t="inlineStr"/>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+4EBA CJK UNIFIED IDEOGRAPH-4EBA | isolated marker/symbol line :: 人</t>
+        </is>
+      </c>
+      <c r="O70" s="1" t="inlineStr"/>
+      <c r="P70" s="1" t="inlineStr"/>
+      <c r="Q70" s="1" t="inlineStr"/>
+      <c r="R70" s="1" t="inlineStr"/>
+      <c r="S70" s="1" t="inlineStr"/>
+      <c r="T70" s="1" t="inlineStr"/>
+      <c r="U70" s="1" t="inlineStr"/>
+      <c r="V70" s="1" t="inlineStr"/>
+      <c r="W70" s="1" t="inlineStr"/>
+      <c r="X70" s="1" t="inlineStr"/>
+      <c r="Y70" s="1" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr"/>
+      <c r="B71" s="1" t="inlineStr"/>
+      <c r="C71" s="1" t="inlineStr"/>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr"/>
+      <c r="F71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr"/>
+      <c r="H71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr"/>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
+      <c r="L71" s="1" t="inlineStr"/>
+      <c r="M71" s="1" t="inlineStr"/>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>L152: isolated marker/symbol line :: 42</t>
+        </is>
+      </c>
+      <c r="O71" s="1" t="inlineStr"/>
+      <c r="P71" s="1" t="inlineStr"/>
+      <c r="Q71" s="1" t="inlineStr"/>
+      <c r="R71" s="1" t="inlineStr"/>
+      <c r="S71" s="1" t="inlineStr"/>
+      <c r="T71" s="1" t="inlineStr"/>
+      <c r="U71" s="1" t="inlineStr"/>
+      <c r="V71" s="1" t="inlineStr"/>
+      <c r="W71" s="1" t="inlineStr"/>
+      <c r="X71" s="1" t="inlineStr"/>
+      <c r="Y71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr"/>
+      <c r="B72" s="1" t="inlineStr"/>
+      <c r="C72" s="1" t="inlineStr"/>
+      <c r="D72" s="1" t="inlineStr"/>
+      <c r="E72" s="1" t="inlineStr"/>
+      <c r="F72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr"/>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
+      <c r="L72" s="1" t="inlineStr"/>
+      <c r="M72" s="1" t="inlineStr"/>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>L154: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="inlineStr"/>
+      <c r="P72" s="1" t="inlineStr"/>
+      <c r="Q72" s="1" t="inlineStr"/>
+      <c r="R72" s="1" t="inlineStr"/>
+      <c r="S72" s="1" t="inlineStr"/>
+      <c r="T72" s="1" t="inlineStr"/>
+      <c r="U72" s="1" t="inlineStr"/>
+      <c r="V72" s="1" t="inlineStr"/>
+      <c r="W72" s="1" t="inlineStr"/>
+      <c r="X72" s="1" t="inlineStr"/>
+      <c r="Y72" s="1" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr"/>
+      <c r="B73" s="1" t="inlineStr"/>
+      <c r="C73" s="1" t="inlineStr"/>
+      <c r="D73" s="1" t="inlineStr"/>
+      <c r="E73" s="1" t="inlineStr"/>
+      <c r="F73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr"/>
+      <c r="H73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr"/>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
+      <c r="L73" s="1" t="inlineStr"/>
+      <c r="M73" s="1" t="inlineStr"/>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>L156: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="inlineStr"/>
+      <c r="P73" s="1" t="inlineStr"/>
+      <c r="Q73" s="1" t="inlineStr"/>
+      <c r="R73" s="1" t="inlineStr"/>
+      <c r="S73" s="1" t="inlineStr"/>
+      <c r="T73" s="1" t="inlineStr"/>
+      <c r="U73" s="1" t="inlineStr"/>
+      <c r="V73" s="1" t="inlineStr"/>
+      <c r="W73" s="1" t="inlineStr"/>
+      <c r="X73" s="1" t="inlineStr"/>
+      <c r="Y73" s="1" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr"/>
+      <c r="B74" s="1" t="inlineStr"/>
+      <c r="C74" s="1" t="inlineStr"/>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr"/>
+      <c r="F74" s="1" t="inlineStr"/>
+      <c r="G74" s="1" t="inlineStr"/>
+      <c r="H74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr"/>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
+      <c r="L74" s="1" t="inlineStr"/>
+      <c r="M74" s="1" t="inlineStr"/>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t>L157: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O74" s="1" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr"/>
+      <c r="Q74" s="1" t="inlineStr"/>
+      <c r="R74" s="1" t="inlineStr"/>
+      <c r="S74" s="1" t="inlineStr"/>
+      <c r="T74" s="1" t="inlineStr"/>
+      <c r="U74" s="1" t="inlineStr"/>
+      <c r="V74" s="1" t="inlineStr"/>
+      <c r="W74" s="1" t="inlineStr"/>
+      <c r="X74" s="1" t="inlineStr"/>
+      <c r="Y74" s="1" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr"/>
+      <c r="B75" s="1" t="inlineStr"/>
+      <c r="C75" s="1" t="inlineStr"/>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr"/>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr"/>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
+      <c r="L75" s="1" t="inlineStr"/>
+      <c r="M75" s="1" t="inlineStr"/>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t>L160: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O75" s="1" t="inlineStr"/>
+      <c r="P75" s="1" t="inlineStr"/>
+      <c r="Q75" s="1" t="inlineStr"/>
+      <c r="R75" s="1" t="inlineStr"/>
+      <c r="S75" s="1" t="inlineStr"/>
+      <c r="T75" s="1" t="inlineStr"/>
+      <c r="U75" s="1" t="inlineStr"/>
+      <c r="V75" s="1" t="inlineStr"/>
+      <c r="W75" s="1" t="inlineStr"/>
+      <c r="X75" s="1" t="inlineStr"/>
+      <c r="Y75" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
